--- a/SGC-CKN/Excel/7cf5dcd9-b5b5-4732-9eb9-7ac095393425_Cọc_khoan_nhồi_C9_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/7cf5dcd9-b5b5-4732-9eb9-7ac095393425_Cọc_khoan_nhồi_C9_D800_20-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>C9</t>
+    <t>P7-141</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/7cf5dcd9-b5b5-4732-9eb9-7ac095393425_Cọc_khoan_nhồi_C9_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/7cf5dcd9-b5b5-4732-9eb9-7ac095393425_Cọc_khoan_nhồi_C9_D800_20-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-141</t>
+    <t>P7-134</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/7cf5dcd9-b5b5-4732-9eb9-7ac095393425_Cọc_khoan_nhồi_C9_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/7cf5dcd9-b5b5-4732-9eb9-7ac095393425_Cọc_khoan_nhồi_C9_D800_20-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>Dự án</t>
   </si>
@@ -143,6 +143,10 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
+    <t xml:space="preserve">18:26
+19/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">19:08
 19/03/2026</t>
   </si>
@@ -171,7 +175,7 @@
 19/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">21:50
+    <t xml:space="preserve">21:30
 19/03/2026</t>
   </si>
   <si>
@@ -181,7 +185,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">21:34
+    <t xml:space="preserve">21:31
 19/03/2026</t>
   </si>
   <si>
@@ -412,11 +416,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
@@ -428,6 +427,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -595,35 +599,35 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,7 +1239,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.95</v>
@@ -1244,10 +1248,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" s="5">
-        <v>3.29</v>
+        <v>6.95</v>
       </c>
       <c r="J11" s="8">
-        <v>7.05</v>
+        <v>14.89</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1334,25 +1338,25 @@
         <v>40</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="15">
         <v>-17.3</v>
       </c>
       <c r="G14" s="15">
-        <v>-24.65</v>
+        <v>-21.65</v>
       </c>
       <c r="H14" s="15">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="I14" s="15">
-        <v>7.35</v>
+        <v>4.35</v>
       </c>
       <c r="J14" s="8">
-        <v>10.26</v>
+        <v>6.21</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1360,22 +1364,22 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" s="18">
-        <v>-24.65</v>
+        <v>-21.65</v>
       </c>
       <c r="G15" s="18">
         <v>-25.75</v>
@@ -1384,135 +1388,135 @@
         <v>0.67</v>
       </c>
       <c r="I15" s="18">
-        <v>1.1</v>
-      </c>
-      <c r="J15" s="21">
-        <v>1.65</v>
+        <v>4.1</v>
+      </c>
+      <c r="J15" s="8">
+        <v>6.15</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="22">
+      <c r="E16" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="21">
         <v>-25.75</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-35.95</v>
       </c>
-      <c r="H16" s="22">
-        <v>1.98</v>
-      </c>
-      <c r="I16" s="22">
+      <c r="H16" s="21">
+        <v>1.65</v>
+      </c>
+      <c r="I16" s="21">
         <v>10.2</v>
       </c>
       <c r="J16" s="8">
-        <v>5.14</v>
-      </c>
-      <c r="K16" s="23" t="s">
+        <v>6.18</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="27" t="s">
+      <c r="C17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="25">
+      <c r="E17" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="24">
         <v>-35.95</v>
       </c>
-      <c r="G17" s="25">
-        <v>-38.5</v>
-      </c>
-      <c r="H17" s="25">
-        <v>0.33</v>
-      </c>
-      <c r="I17" s="25">
-        <v>2.55</v>
+      <c r="G17" s="24">
+        <v>-38.3</v>
+      </c>
+      <c r="H17" s="24">
+        <v>0.38</v>
+      </c>
+      <c r="I17" s="24">
+        <v>2.35</v>
       </c>
       <c r="J17" s="8">
-        <v>7.65</v>
-      </c>
-      <c r="K17" s="26" t="s">
+        <v>6.13</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="A18" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="30" t="s">
+      <c r="C18" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="D18" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="28">
-        <v>-38.5</v>
-      </c>
-      <c r="G18" s="28">
+      <c r="E18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="27">
+        <v>-38.3</v>
+      </c>
+      <c r="G18" s="27">
         <v>-39.8</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <v>0.83</v>
       </c>
-      <c r="I18" s="28">
-        <v>1.3</v>
-      </c>
-      <c r="J18" s="21">
-        <v>1.56</v>
-      </c>
-      <c r="K18" s="29" t="s">
+      <c r="I18" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="J18" s="30">
+        <v>1.8</v>
+      </c>
+      <c r="K18" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>-39.8</v>
@@ -1526,7 +1530,7 @@
       <c r="I19" s="31">
         <v>4.35</v>
       </c>
-      <c r="J19" s="21">
+      <c r="J19" s="30">
         <v>2.42</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1535,19 +1539,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" s="34">
         <v>-44.15</v>
@@ -1561,7 +1565,7 @@
       <c r="I20" s="34">
         <v>0.9</v>
       </c>
-      <c r="J20" s="21">
+      <c r="J20" s="30">
         <v>2.08</v>
       </c>
       <c r="K20" s="35" t="s">
@@ -1570,7 +1574,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1676,31 +1680,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1717,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.95</v>
@@ -1726,10 +1730,10 @@
         <v>0.47</v>
       </c>
       <c r="H2" s="5">
-        <v>3.29</v>
+        <v>6.95</v>
       </c>
       <c r="I2" s="8">
-        <v>7.05</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1807,16 +1811,16 @@
         <v>-17.3</v>
       </c>
       <c r="F5" s="15">
-        <v>-24.65</v>
+        <v>-21.65</v>
       </c>
       <c r="G5" s="15">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H5" s="15">
-        <v>7.35</v>
+        <v>4.35</v>
       </c>
       <c r="I5" s="8">
-        <v>10.26</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1827,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>-24.65</v>
+        <v>-21.65</v>
       </c>
       <c r="F6" s="18">
         <v>-25.75</v>
@@ -1842,97 +1846,97 @@
         <v>0.67</v>
       </c>
       <c r="H6" s="18">
-        <v>1.1</v>
-      </c>
-      <c r="I6" s="21">
+        <v>4.1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="21">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21">
+        <v>-25.75</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-35.95</v>
+      </c>
+      <c r="G7" s="21">
         <v>1.65</v>
       </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
-        <v>6</v>
-      </c>
-      <c r="B7" s="22" t="s">
+      <c r="H7" s="21">
+        <v>10.2</v>
+      </c>
+      <c r="I7" s="8">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C8" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
-        <v>-25.75</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E8" s="24">
         <v>-35.95</v>
       </c>
-      <c r="G7" s="22">
-        <v>1.98</v>
-      </c>
-      <c r="H7" s="22">
-        <v>10.2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>5.14</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>7</v>
-      </c>
-      <c r="B8" s="25" t="s">
+      <c r="F8" s="24">
+        <v>-38.3</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0.38</v>
+      </c>
+      <c r="H8" s="24">
+        <v>2.35</v>
+      </c>
+      <c r="I8" s="8">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <v>8</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="C9" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="27">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
-        <v>-35.95</v>
-      </c>
-      <c r="F8" s="25">
-        <v>-38.5</v>
-      </c>
-      <c r="G8" s="25">
-        <v>0.33</v>
-      </c>
-      <c r="H8" s="25">
-        <v>2.55</v>
-      </c>
-      <c r="I8" s="8">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>8</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="28">
-        <v>1</v>
-      </c>
-      <c r="E9" s="28">
-        <v>-38.5</v>
-      </c>
-      <c r="F9" s="28">
+      <c r="E9" s="27">
+        <v>-38.3</v>
+      </c>
+      <c r="F9" s="27">
         <v>-39.8</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <v>0.83</v>
       </c>
-      <c r="H9" s="28">
-        <v>1.3</v>
-      </c>
-      <c r="I9" s="21">
-        <v>1.56</v>
+      <c r="H9" s="27">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="30">
+        <v>1.8</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1943,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1960,7 +1964,7 @@
       <c r="H10" s="31">
         <v>4.35</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="30">
         <v>2.42</v>
       </c>
     </row>
@@ -1972,7 +1976,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1989,13 +1993,13 @@
       <c r="H11" s="34">
         <v>0.9</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="30">
         <v>2.08</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2007,19 +2011,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-45.05</v>
       </c>
       <c r="G12" s="39">
-        <v>8.48</v>
+        <v>8.18</v>
       </c>
       <c r="H12" s="39">
-        <v>41.39</v>
+        <v>45.05</v>
       </c>
       <c r="I12" s="39">
-        <v>4.88</v>
+        <v>5.51</v>
       </c>
     </row>
   </sheetData>
